--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MARYLAND_2021.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2021/MARYLAND_2021.xlsx
@@ -1734,7 +1734,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C77">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C118">
@@ -5892,7 +5892,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C308">
@@ -6144,7 +6144,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C322">
